--- a/docs/hardware/mechanical/master_bom.xlsx
+++ b/docs/hardware/mechanical/master_bom.xlsx
@@ -25,7 +25,7 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="E20" authorId="0">
+    <comment ref="E21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -38,7 +38,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E22" authorId="0">
+    <comment ref="E23" authorId="0">
       <text>
         <r>
           <rPr>
@@ -51,7 +51,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E24" authorId="0">
+    <comment ref="E25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -64,7 +64,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I28" authorId="0">
+    <comment ref="I29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -77,7 +77,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J34" authorId="0">
+    <comment ref="J35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="133">
   <si>
     <t xml:space="preserve">Status</t>
   </si>
@@ -109,7 +109,7 @@
     <t xml:space="preserve">Item Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Per Board Quantity</t>
+    <t xml:space="preserve">Per SparkNode Quantity</t>
   </si>
   <si>
     <t xml:space="preserve">Total Quantity Needed</t>
@@ -163,6 +163,9 @@
     <t xml:space="preserve">Body</t>
   </si>
   <si>
+    <t xml:space="preserve">Hall-effect sensor board (for wheel rotation counting)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dagu DG01D 48:1 motor (sold in pairs)</t>
   </si>
   <si>
@@ -421,7 +424,10 @@
     <t xml:space="preserve">https://au.element14.com/vishay/k104z15y5ve5tl2/bc-components-part-number/dp/3322180</t>
   </si>
   <si>
-    <t xml:space="preserve">XXXXX hall-effect sensor (TBC)</t>
+    <t xml:space="preserve">DRV5033AJQLPGM hall-effect sensor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Omnipolar hall-effect switch</t>
   </si>
   <si>
     <t xml:space="preserve">4.7nf</t>
@@ -1064,7 +1070,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AC1016"/>
+  <dimension ref="A1:AC1017"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.5"/>
@@ -1152,7 +1158,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="12" t="n">
-        <f aca="false">$E$49*D2</f>
+        <f aca="false">$E$50*D2</f>
         <v>5</v>
       </c>
       <c r="F2" s="12"/>
@@ -1183,7 +1189,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="12" t="n">
-        <f aca="false">$E$49*D3</f>
+        <f aca="false">$E$50*D3</f>
         <v>5</v>
       </c>
       <c r="F3" s="12"/>
@@ -1204,101 +1210,98 @@
       <c r="M3" s="10"/>
     </row>
     <row r="4" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16"/>
       <c r="B4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="18" t="n">
-        <f aca="false">$E$49*D4</f>
+      <c r="E4" s="12" t="n">
+        <f aca="false">$E$50*D4</f>
         <v>5</v>
       </c>
-      <c r="F4" s="18"/>
-      <c r="G4" s="19" t="n">
-        <v>10</v>
+      <c r="F4" s="12"/>
+      <c r="G4" s="13" t="n">
+        <v>3</v>
       </c>
       <c r="H4" s="13" t="n">
         <f aca="false">E4*G4</f>
-        <v>50</v>
-      </c>
-      <c r="J4" s="20"/>
-      <c r="K4" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="N4" s="10" t="s">
-        <v>24</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="M4" s="10"/>
     </row>
     <row r="5" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16"/>
       <c r="B5" s="10" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D5" s="18" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="18" t="n">
-        <f aca="false">$E$49*D5</f>
+        <f aca="false">$E$50*D5</f>
         <v>5</v>
       </c>
       <c r="F5" s="18"/>
       <c r="G5" s="19" t="n">
-        <v>17.49</v>
+        <v>10</v>
       </c>
       <c r="H5" s="13" t="n">
         <f aca="false">E5*G5</f>
-        <v>87.45</v>
+        <v>50</v>
       </c>
       <c r="J5" s="20"/>
-      <c r="K5" s="21"/>
+      <c r="K5" s="21" t="s">
+        <v>23</v>
+      </c>
       <c r="L5" s="21" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16"/>
       <c r="B6" s="10" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D6" s="18" t="n">
         <v>1</v>
       </c>
       <c r="E6" s="18" t="n">
-        <f aca="false">$E$49*D6</f>
+        <f aca="false">$E$50*D6</f>
         <v>5</v>
       </c>
       <c r="F6" s="18"/>
       <c r="G6" s="19" t="n">
-        <v>4.7</v>
+        <v>17.49</v>
       </c>
       <c r="H6" s="13" t="n">
         <f aca="false">E6*G6</f>
-        <v>23.5</v>
+        <v>87.45</v>
       </c>
       <c r="J6" s="20"/>
       <c r="K6" s="21"/>
       <c r="L6" s="21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N6" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1307,492 +1310,483 @@
         <v>20</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="18" t="n">
-        <f aca="false">$E$49*D7</f>
-        <v>10</v>
+        <f aca="false">$E$50*D7</f>
+        <v>5</v>
       </c>
       <c r="F7" s="18"/>
       <c r="G7" s="19" t="n">
-        <v>0.75</v>
+        <v>4.7</v>
       </c>
       <c r="H7" s="13" t="n">
         <f aca="false">E7*G7</f>
-        <v>7.5</v>
+        <v>23.5</v>
       </c>
       <c r="J7" s="20"/>
       <c r="K7" s="21"/>
       <c r="L7" s="21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N7" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" s="9" customFormat="true" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16"/>
       <c r="B8" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D8" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" s="18" t="n">
-        <f aca="false">$E$49*D8</f>
-        <v>5</v>
+        <f aca="false">$E$50*D8</f>
+        <v>10</v>
       </c>
       <c r="F8" s="18"/>
       <c r="G8" s="19" t="n">
-        <v>20</v>
+        <v>0.75</v>
       </c>
       <c r="H8" s="13" t="n">
         <f aca="false">E8*G8</f>
-        <v>100</v>
-      </c>
-      <c r="I8" s="22" t="s">
-        <v>33</v>
+        <v>7.5</v>
       </c>
       <c r="J8" s="20"/>
       <c r="K8" s="21"/>
       <c r="L8" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="N8" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
-    </row>
-    <row r="9" s="9" customFormat="true" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
-        <v>35</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" s="9" customFormat="true" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="16"/>
       <c r="B9" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="10" t="s">
-        <v>36</v>
+      <c r="C9" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="D9" s="18" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="E9" s="18" t="n">
-        <f aca="false">$E$49*D9</f>
-        <v>195</v>
+        <f aca="false">$E$50*D9</f>
+        <v>5</v>
       </c>
       <c r="F9" s="18"/>
-      <c r="G9" s="13" t="n">
-        <v>0.25</v>
+      <c r="G9" s="19" t="n">
+        <v>20</v>
       </c>
       <c r="H9" s="13" t="n">
         <f aca="false">E9*G9</f>
-        <v>48.75</v>
-      </c>
-      <c r="J9" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="I9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J9" s="20"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="O9" s="23"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
+    </row>
+    <row r="10" s="9" customFormat="true" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="K9" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="L9" s="21" t="s">
+      <c r="D10" s="18" t="n">
         <v>39</v>
       </c>
-      <c r="M9" s="26" t="n">
-        <v>1841425</v>
-      </c>
-      <c r="N9" s="27" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" s="9" customFormat="true" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="12" t="n">
-        <f aca="false">$E$49*D10</f>
-        <v>5</v>
-      </c>
-      <c r="F10" s="12" t="n">
-        <v>20</v>
-      </c>
+      <c r="E10" s="18" t="n">
+        <f aca="false">$E$50*D10</f>
+        <v>195</v>
+      </c>
+      <c r="F10" s="18"/>
       <c r="G10" s="13" t="n">
-        <v>13</v>
+        <v>0.25</v>
       </c>
       <c r="H10" s="13" t="n">
         <f aca="false">E10*G10</f>
-        <v>65</v>
-      </c>
-      <c r="I10" s="11"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15" t="s">
-        <v>26</v>
+        <v>48.75</v>
+      </c>
+      <c r="J10" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="K10" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="L10" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="M10" s="26" t="n">
+        <v>1841425</v>
       </c>
       <c r="N10" s="27" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" s="9" customFormat="true" ht="20.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" s="9" customFormat="true" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="17" t="s">
-        <v>44</v>
+      <c r="C11" s="15" t="s">
+        <v>43</v>
       </c>
       <c r="D11" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="12" t="n">
-        <f aca="false">$E$49*D11</f>
+        <f aca="false">$E$50*D11</f>
         <v>5</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>17.14</v>
+        <v>13</v>
       </c>
       <c r="H11" s="13" t="n">
         <f aca="false">E11*G11</f>
-        <v>85.7</v>
-      </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="K11" s="15" t="s">
-        <v>46</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="I11" s="11"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
       <c r="L11" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="M11" s="10"/>
-      <c r="N11" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="O11" s="29"/>
-      <c r="P11" s="29"/>
-      <c r="Q11" s="29"/>
-      <c r="R11" s="29"/>
-      <c r="S11" s="29"/>
-      <c r="T11" s="29"/>
-    </row>
-    <row r="12" s="9" customFormat="true" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>27</v>
+      </c>
+      <c r="N11" s="27" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" s="9" customFormat="true" ht="20.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="18" t="n">
+      <c r="C12" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="18" t="n">
-        <f aca="false">$E$49*D12</f>
+      <c r="E12" s="12" t="n">
+        <f aca="false">$E$50*D12</f>
         <v>5</v>
       </c>
-      <c r="F12" s="18" t="n">
-        <v>16</v>
+      <c r="F12" s="12" t="n">
+        <v>7</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>1.72</v>
+        <v>17.14</v>
       </c>
       <c r="H12" s="13" t="n">
         <f aca="false">E12*G12</f>
-        <v>8.6</v>
-      </c>
-      <c r="J12" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="K12" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="L12" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="M12" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="N12" s="27" t="s">
-        <v>52</v>
-      </c>
+        <v>85.7</v>
+      </c>
+      <c r="I12" s="10"/>
+      <c r="J12" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="M12" s="10"/>
+      <c r="N12" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="O12" s="29"/>
+      <c r="P12" s="29"/>
+      <c r="Q12" s="29"/>
+      <c r="R12" s="29"/>
+      <c r="S12" s="29"/>
+      <c r="T12" s="29"/>
     </row>
     <row r="13" s="9" customFormat="true" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D13" s="18" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="18" t="n">
-        <f aca="false">$E$49*D13</f>
+        <f aca="false">$E$50*D13</f>
         <v>5</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>0.508</v>
+        <v>1.72</v>
       </c>
       <c r="H13" s="13" t="n">
         <f aca="false">E13*G13</f>
-        <v>2.54</v>
-      </c>
-      <c r="J13" s="25" t="s">
-        <v>54</v>
+        <v>8.6</v>
+      </c>
+      <c r="J13" s="21" t="s">
+        <v>50</v>
       </c>
       <c r="K13" s="21" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="L13" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="M13" s="26" t="n">
-        <v>1360787</v>
+        <v>40</v>
+      </c>
+      <c r="M13" s="18" t="s">
+        <v>52</v>
       </c>
       <c r="N13" s="27" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" s="9" customFormat="true" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E14" s="18" t="n">
-        <f aca="false">$E$49*D14</f>
-        <v>30</v>
+        <f aca="false">$E$50*D14</f>
+        <v>5</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>125</v>
+        <v>27</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>0.131</v>
+        <v>0.508</v>
       </c>
       <c r="H14" s="13" t="n">
         <f aca="false">E14*G14</f>
-        <v>3.93</v>
-      </c>
-      <c r="J14" s="21" t="s">
-        <v>58</v>
+        <v>2.54</v>
+      </c>
+      <c r="J14" s="25" t="s">
+        <v>55</v>
       </c>
       <c r="K14" s="21" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L14" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="M14" s="18" t="n">
-        <v>1593458</v>
+        <v>40</v>
+      </c>
+      <c r="M14" s="26" t="n">
+        <v>1360787</v>
       </c>
       <c r="N14" s="27" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" s="9" customFormat="true" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E15" s="18" t="n">
-        <f aca="false">$E$49*D15</f>
-        <v>15</v>
+        <f aca="false">$E$50*D15</f>
+        <v>30</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0.287</v>
+        <v>0.131</v>
       </c>
       <c r="H15" s="13" t="n">
         <f aca="false">E15*G15</f>
-        <v>4.305</v>
+        <v>3.93</v>
       </c>
       <c r="J15" s="21" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K15" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M15" s="18" t="n">
-        <v>1593460</v>
+        <v>1593458</v>
       </c>
       <c r="N15" s="27" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" s="9" customFormat="true" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>14</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="18" t="n">
-        <f aca="false">$E$49*D16</f>
-        <v>5</v>
+        <f aca="false">$E$50*D16</f>
+        <v>15</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>0.271</v>
+        <v>0.287</v>
       </c>
       <c r="H16" s="13" t="n">
         <f aca="false">E16*G16</f>
-        <v>1.355</v>
+        <v>4.305</v>
       </c>
       <c r="J16" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="K16" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="L16" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="M16" s="18" t="n">
+        <v>1593460</v>
+      </c>
+      <c r="N16" s="27" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" s="9" customFormat="true" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="K16" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="L16" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="M16" s="18" t="n">
-        <v>1593461</v>
-      </c>
-      <c r="N16" s="27" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11"/>
-      <c r="B17" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>68</v>
-      </c>
       <c r="D17" s="18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" s="18" t="n">
-        <f aca="false">$E$49*D17</f>
-        <v>15</v>
+        <f aca="false">$E$50*D17</f>
+        <v>5</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>0.335</v>
+        <v>0.271</v>
       </c>
       <c r="H17" s="13" t="n">
         <f aca="false">E17*G17</f>
-        <v>5.025</v>
+        <v>1.355</v>
       </c>
       <c r="J17" s="21" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K17" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L17" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>1593463</v>
+        <v>1593461</v>
       </c>
       <c r="N17" s="27" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11"/>
       <c r="B18" s="10" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D18" s="18" t="n">
         <v>3</v>
       </c>
       <c r="E18" s="18" t="n">
-        <f aca="false">$E$49*D18</f>
+        <f aca="false">$E$50*D18</f>
         <v>15</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>0.743</v>
+        <v>0.335</v>
       </c>
       <c r="H18" s="13" t="n">
         <f aca="false">E18*G18</f>
-        <v>11.145</v>
-      </c>
-      <c r="J18" s="21" t="n">
-        <v>61900211021</v>
+        <v>5.025</v>
+      </c>
+      <c r="J18" s="21" t="s">
+        <v>70</v>
       </c>
       <c r="K18" s="21" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="L18" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M18" s="18" t="n">
-        <v>1841368</v>
+        <v>1593463</v>
       </c>
       <c r="N18" s="27" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1801,681 +1795,701 @@
         <v>14</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" s="18" t="n">
-        <f aca="false">$E$49*D19</f>
-        <v>10</v>
+        <f aca="false">$E$50*D19</f>
+        <v>15</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>0.88</v>
+        <v>0.743</v>
       </c>
       <c r="H19" s="13" t="n">
         <f aca="false">E19*G19</f>
-        <v>8.8</v>
+        <v>11.145</v>
       </c>
       <c r="J19" s="21" t="n">
-        <v>61900211121</v>
+        <v>61900211021</v>
       </c>
       <c r="K19" s="21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L19" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M19" s="18" t="n">
-        <v>1841369</v>
+        <v>1841368</v>
       </c>
       <c r="N19" s="27" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11"/>
       <c r="B20" s="10" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D20" s="18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E20" s="18" t="n">
-        <f aca="false">$E$49*D20</f>
-        <v>25</v>
+        <f aca="false">$E$50*D20</f>
+        <v>10</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>183</v>
+        <v>31</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>0.223</v>
+        <v>0.88</v>
       </c>
       <c r="H20" s="13" t="n">
         <f aca="false">E20*G20</f>
-        <v>5.575</v>
-      </c>
-      <c r="J20" s="25" t="n">
-        <v>61900211621</v>
+        <v>8.8</v>
+      </c>
+      <c r="J20" s="21" t="n">
+        <v>61900211121</v>
       </c>
       <c r="K20" s="21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L20" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="M20" s="26" t="n">
-        <v>1841370</v>
+        <v>40</v>
+      </c>
+      <c r="M20" s="18" t="n">
+        <v>1841369</v>
       </c>
       <c r="N20" s="27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11"/>
       <c r="B21" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>78</v>
+        <v>20</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>76</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E21" s="18" t="n">
-        <f aca="false">$E$49*D21</f>
-        <v>10</v>
+        <f aca="false">$E$50*D21</f>
+        <v>25</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>52</v>
+        <v>183</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>1.46</v>
+        <v>0.223</v>
       </c>
       <c r="H21" s="13" t="n">
         <f aca="false">E21*G21</f>
-        <v>14.6</v>
-      </c>
-      <c r="J21" s="21" t="n">
-        <v>61900411121</v>
+        <v>5.575</v>
+      </c>
+      <c r="J21" s="25" t="n">
+        <v>61900211621</v>
       </c>
       <c r="K21" s="21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="M21" s="18" t="n">
-        <v>1841378</v>
+        <v>40</v>
+      </c>
+      <c r="M21" s="26" t="n">
+        <v>1841370</v>
       </c>
       <c r="N21" s="27" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11"/>
       <c r="B22" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>80</v>
+        <v>78</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>79</v>
       </c>
       <c r="D22" s="18" t="n">
         <v>2</v>
       </c>
       <c r="E22" s="18" t="n">
-        <f aca="false">$E$49*D22</f>
+        <f aca="false">$E$50*D22</f>
         <v>10</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>400</v>
+        <v>52</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>0.296</v>
+        <v>1.46</v>
       </c>
       <c r="H22" s="13" t="n">
         <f aca="false">E22*G22</f>
-        <v>2.96</v>
-      </c>
-      <c r="J22" s="25" t="n">
-        <v>61900411621</v>
+        <v>14.6</v>
+      </c>
+      <c r="J22" s="21" t="n">
+        <v>61900411121</v>
       </c>
       <c r="K22" s="21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="M22" s="26" t="n">
-        <v>1841379</v>
+        <v>40</v>
+      </c>
+      <c r="M22" s="18" t="n">
+        <v>1841378</v>
       </c>
       <c r="N22" s="27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11"/>
       <c r="B23" s="10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="18" t="n">
-        <f aca="false">$E$49*D23</f>
-        <v>5</v>
+        <f aca="false">$E$50*D23</f>
+        <v>10</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>21</v>
+        <v>400</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>1.91</v>
+        <v>0.296</v>
       </c>
       <c r="H23" s="13" t="n">
         <f aca="false">E23*G23</f>
-        <v>9.55</v>
-      </c>
-      <c r="J23" s="21" t="n">
-        <v>61900511121</v>
+        <v>2.96</v>
+      </c>
+      <c r="J23" s="25" t="n">
+        <v>61900411621</v>
       </c>
       <c r="K23" s="21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L23" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="M23" s="18" t="n">
-        <v>1841382</v>
+        <v>40</v>
+      </c>
+      <c r="M23" s="26" t="n">
+        <v>1841379</v>
       </c>
       <c r="N23" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11"/>
       <c r="B24" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D24" s="18" t="n">
         <v>1</v>
       </c>
       <c r="E24" s="18" t="n">
-        <f aca="false">$E$49*D24</f>
+        <f aca="false">$E$50*D24</f>
         <v>5</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>200</v>
+        <v>21</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>0.29</v>
+        <v>1.91</v>
       </c>
       <c r="H24" s="13" t="n">
         <f aca="false">E24*G24</f>
-        <v>1.45</v>
-      </c>
-      <c r="J24" s="25" t="n">
-        <v>61900511621</v>
+        <v>9.55</v>
+      </c>
+      <c r="J24" s="21" t="n">
+        <v>61900511121</v>
       </c>
       <c r="K24" s="21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L24" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="M24" s="26" t="n">
-        <v>1841383</v>
+        <v>40</v>
+      </c>
+      <c r="M24" s="18" t="n">
+        <v>1841382</v>
       </c>
       <c r="N24" s="27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11"/>
       <c r="B25" s="10" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D25" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="18" t="n">
-        <f aca="false">$E$49*D25</f>
-        <v>10</v>
+        <f aca="false">$E$50*D25</f>
+        <v>5</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>37</v>
+        <v>200</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>1.13</v>
+        <v>0.29</v>
       </c>
       <c r="H25" s="13" t="n">
         <f aca="false">E25*G25</f>
-        <v>11.3</v>
-      </c>
-      <c r="J25" s="21" t="n">
-        <v>61900811021</v>
+        <v>1.45</v>
+      </c>
+      <c r="J25" s="25" t="n">
+        <v>61900511621</v>
       </c>
       <c r="K25" s="21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L25" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="M25" s="18" t="n">
-        <v>3818035</v>
-      </c>
-      <c r="N25" s="30" t="s">
-        <v>87</v>
+        <v>40</v>
+      </c>
+      <c r="M25" s="26" t="n">
+        <v>1841383</v>
+      </c>
+      <c r="N25" s="27" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="26" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11"/>
       <c r="B26" s="10" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D26" s="18" t="n">
         <v>2</v>
       </c>
       <c r="E26" s="18" t="n">
-        <f aca="false">$E$49*D26</f>
+        <f aca="false">$E$50*D26</f>
         <v>10</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>0.512</v>
+        <v>1.13</v>
       </c>
       <c r="H26" s="13" t="n">
         <f aca="false">E26*G26</f>
-        <v>5.12</v>
-      </c>
-      <c r="J26" s="25" t="n">
-        <v>61900811621</v>
+        <v>11.3</v>
+      </c>
+      <c r="J26" s="21" t="n">
+        <v>61900811021</v>
       </c>
       <c r="K26" s="21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L26" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="M26" s="26" t="n">
-        <v>3818418</v>
-      </c>
-      <c r="N26" s="27" t="s">
-        <v>89</v>
+        <v>40</v>
+      </c>
+      <c r="M26" s="18" t="n">
+        <v>3818035</v>
+      </c>
+      <c r="N26" s="30" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="27" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11"/>
       <c r="B27" s="10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D27" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="18" t="n">
-        <f aca="false">$E$49*D27</f>
-        <v>5</v>
+        <f aca="false">$E$50*D27</f>
+        <v>10</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>0.22</v>
+        <v>0.512</v>
       </c>
       <c r="H27" s="13" t="n">
         <f aca="false">E27*G27</f>
-        <v>1.1</v>
-      </c>
-      <c r="J27" s="21" t="s">
-        <v>91</v>
+        <v>5.12</v>
+      </c>
+      <c r="J27" s="25" t="n">
+        <v>61900811621</v>
       </c>
       <c r="K27" s="21" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="L27" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="M27" s="18" t="n">
-        <v>947167701</v>
+        <v>40</v>
+      </c>
+      <c r="M27" s="26" t="n">
+        <v>3818418</v>
       </c>
       <c r="N27" s="27" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="28" s="9" customFormat="true" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11"/>
       <c r="B28" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="D28" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E28" s="12" t="n">
-        <f aca="false">$E$49*D28</f>
-        <v>15</v>
-      </c>
-      <c r="F28" s="12"/>
+        <v>18</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <f aca="false">$E$50*D28</f>
+        <v>5</v>
+      </c>
+      <c r="F28" s="18" t="n">
+        <v>24</v>
+      </c>
       <c r="G28" s="13" t="n">
-        <v>0.186</v>
+        <v>0.22</v>
       </c>
       <c r="H28" s="13" t="n">
         <f aca="false">E28*G28</f>
-        <v>2.79</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15" t="s">
-        <v>39</v>
+        <v>1.1</v>
+      </c>
+      <c r="J28" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="K28" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="L28" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="M28" s="18" t="n">
+        <v>947167701</v>
       </c>
       <c r="N28" s="27" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" s="9" customFormat="true" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11"/>
       <c r="B29" s="10" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" s="12" t="n">
-        <f aca="false">$E$49*D29</f>
-        <v>10</v>
-      </c>
-      <c r="F29" s="12" t="n">
-        <v>30</v>
-      </c>
+        <f aca="false">$E$50*D29</f>
+        <v>15</v>
+      </c>
+      <c r="F29" s="12"/>
       <c r="G29" s="13" t="n">
-        <v>0.18</v>
+        <v>0.186</v>
       </c>
       <c r="H29" s="13" t="n">
         <f aca="false">E29*G29</f>
-        <v>1.8</v>
+        <v>2.79</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="J29" s="31" t="n">
-        <v>7510110</v>
-      </c>
-      <c r="K29" s="15" t="s">
-        <v>98</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
       <c r="L29" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="M29" s="12" t="n">
-        <v>1453528</v>
+        <v>40</v>
       </c>
       <c r="N29" s="27" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="30" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="30" s="9" customFormat="true" ht="20.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11"/>
       <c r="B30" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C30" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="D30" s="18" t="n">
+      <c r="C30" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="D30" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="E30" s="18" t="n">
-        <f aca="false">$E$49*D30</f>
+      <c r="E30" s="12" t="n">
+        <f aca="false">$E$50*D30</f>
         <v>10</v>
       </c>
-      <c r="F30" s="18" t="n">
-        <v>21</v>
-      </c>
-      <c r="G30" s="19" t="n">
-        <v>5.05</v>
+      <c r="F30" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>0.18</v>
       </c>
       <c r="H30" s="13" t="n">
         <f aca="false">E30*G30</f>
-        <v>50.5</v>
-      </c>
-      <c r="J30" s="20"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="N30" s="10" t="s">
-        <v>101</v>
+        <v>1.8</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="J30" s="31" t="n">
+        <v>7510110</v>
+      </c>
+      <c r="K30" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="L30" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="M30" s="12" t="n">
+        <v>1453528</v>
+      </c>
+      <c r="N30" s="27" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="31" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11"/>
       <c r="B31" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>102</v>
+        <v>14</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>101</v>
       </c>
       <c r="D31" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" s="18" t="n">
-        <f aca="false">$E$49*D31</f>
-        <v>5</v>
+        <f aca="false">$E$50*D31</f>
+        <v>10</v>
       </c>
       <c r="F31" s="18" t="n">
-        <v>14</v>
-      </c>
-      <c r="G31" s="32" t="n">
-        <v>0.05</v>
+        <v>21</v>
+      </c>
+      <c r="G31" s="19" t="n">
+        <v>5.05</v>
       </c>
       <c r="H31" s="13" t="n">
         <f aca="false">E31*G31</f>
-        <v>0.25</v>
-      </c>
-      <c r="I31" s="33"/>
+        <v>50.5</v>
+      </c>
       <c r="J31" s="20"/>
       <c r="K31" s="21"/>
-      <c r="L31" s="21"/>
-      <c r="N31" s="10"/>
+      <c r="L31" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="N31" s="10" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="32" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="11"/>
       <c r="B32" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="15" t="s">
         <v>103</v>
       </c>
       <c r="D32" s="18" t="n">
         <v>1</v>
       </c>
       <c r="E32" s="18" t="n">
-        <f aca="false">$E$49*D32</f>
+        <f aca="false">$E$50*D32</f>
         <v>5</v>
       </c>
-      <c r="F32" s="18"/>
-      <c r="G32" s="13" t="n">
-        <v>0.18</v>
+      <c r="F32" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="G32" s="32" t="n">
+        <v>0.05</v>
       </c>
       <c r="H32" s="13" t="n">
         <f aca="false">E32*G32</f>
-        <v>0.9</v>
-      </c>
-      <c r="J32" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="K32" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="L32" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="M32" s="18" t="n">
-        <v>3322180</v>
-      </c>
-      <c r="N32" s="27" t="s">
-        <v>106</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="I32" s="33"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="21"/>
+      <c r="L32" s="21"/>
+      <c r="N32" s="10"/>
     </row>
     <row r="33" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>107</v>
+        <v>18</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>104</v>
       </c>
       <c r="D33" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E33" s="12" t="n">
-        <f aca="false">$E$49*D33</f>
-        <v>10</v>
-      </c>
-      <c r="F33" s="12"/>
-      <c r="G33" s="13"/>
+        <v>1</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <f aca="false">$E$50*D33</f>
+        <v>5</v>
+      </c>
+      <c r="F33" s="18"/>
+      <c r="G33" s="13" t="n">
+        <v>0.18</v>
+      </c>
       <c r="H33" s="13" t="n">
         <f aca="false">E33*G33</f>
-        <v>0</v>
-      </c>
-      <c r="J33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
-      <c r="M33" s="18"/>
-      <c r="N33" s="27"/>
-    </row>
-    <row r="34" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.9</v>
+      </c>
+      <c r="J33" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="K33" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="L33" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="M33" s="18" t="n">
+        <v>3322180</v>
+      </c>
+      <c r="N33" s="27" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="34" s="9" customFormat="true" ht="30.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="D34" s="18" t="n">
-        <v>4</v>
+      <c r="D34" s="12" t="n">
+        <v>2</v>
       </c>
       <c r="E34" s="12" t="n">
-        <f aca="false">$E$49*D34</f>
-        <v>20</v>
-      </c>
-      <c r="F34" s="12"/>
+        <f aca="false">$E$50*D34</f>
+        <v>10</v>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>98</v>
+      </c>
       <c r="G34" s="13" t="n">
         <v>0.18</v>
       </c>
       <c r="H34" s="13" t="n">
         <f aca="false">E34*G34</f>
-        <v>3.6</v>
-      </c>
-      <c r="J34" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="K34" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="L34" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="M34" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="N34" s="27" t="s">
+        <v>1.8</v>
+      </c>
+      <c r="I34" s="22" t="s">
         <v>109</v>
       </c>
+      <c r="J34" s="21"/>
+      <c r="K34" s="21"/>
+      <c r="L34" s="21"/>
+      <c r="M34" s="18"/>
+      <c r="N34" s="27"/>
     </row>
     <row r="35" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C35" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" s="15" t="s">
         <v>110</v>
       </c>
       <c r="D35" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="18" t="n">
-        <f aca="false">$E$49*D35</f>
-        <v>5</v>
-      </c>
-      <c r="F35" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="E35" s="12" t="n">
+        <f aca="false">$E$50*D35</f>
+        <v>20</v>
+      </c>
+      <c r="F35" s="12"/>
       <c r="G35" s="13" t="n">
         <v>0.18</v>
       </c>
       <c r="H35" s="13" t="n">
         <f aca="false">E35*G35</f>
-        <v>0.9</v>
-      </c>
-      <c r="J35" s="20"/>
-      <c r="K35" s="21"/>
-      <c r="L35" s="21"/>
+        <v>3.6</v>
+      </c>
+      <c r="J35" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="K35" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="L35" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="M35" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="N35" s="27" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="36" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>111</v>
+        <v>18</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>112</v>
       </c>
       <c r="D36" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" s="18" t="n">
-        <f aca="false">$E$49*D36</f>
-        <v>10</v>
+        <f aca="false">$E$50*D36</f>
+        <v>5</v>
       </c>
       <c r="F36" s="18"/>
-      <c r="G36" s="32" t="n">
-        <v>0</v>
+      <c r="G36" s="13" t="n">
+        <v>0.18</v>
       </c>
       <c r="H36" s="13" t="n">
         <f aca="false">E36*G36</f>
-        <v>0</v>
-      </c>
-      <c r="I36" s="33"/>
+        <v>0.9</v>
+      </c>
       <c r="J36" s="20"/>
       <c r="K36" s="21"/>
       <c r="L36" s="21"/>
-      <c r="N36" s="10"/>
     </row>
     <row r="37" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D37" s="18" t="n">
         <v>2</v>
       </c>
       <c r="E37" s="18" t="n">
-        <f aca="false">$E$49*D37</f>
+        <f aca="false">$E$50*D37</f>
         <v>10</v>
       </c>
       <c r="F37" s="18"/>
@@ -2493,20 +2507,20 @@
       <c r="N37" s="10"/>
     </row>
     <row r="38" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>113</v>
+      <c r="B38" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>114</v>
       </c>
       <c r="D38" s="18" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E38" s="18" t="n">
-        <f aca="false">$E$49*D38</f>
-        <v>60</v>
-      </c>
-      <c r="F38" s="33"/>
+        <f aca="false">$E$50*D38</f>
+        <v>10</v>
+      </c>
+      <c r="F38" s="18"/>
       <c r="G38" s="32" t="n">
         <v>0</v>
       </c>
@@ -2514,9 +2528,7 @@
         <f aca="false">E38*G38</f>
         <v>0</v>
       </c>
-      <c r="I38" s="9" t="s">
-        <v>114</v>
-      </c>
+      <c r="I38" s="33"/>
       <c r="J38" s="20"/>
       <c r="K38" s="21"/>
       <c r="L38" s="21"/>
@@ -2530,15 +2542,20 @@
         <v>115</v>
       </c>
       <c r="D39" s="18" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E39" s="18" t="n">
-        <f aca="false">$E$49*D39</f>
-        <v>20</v>
+        <f aca="false">$E$50*D39</f>
+        <v>60</v>
       </c>
       <c r="F39" s="33"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="13"/>
+      <c r="G39" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="13" t="n">
+        <f aca="false">E39*G39</f>
+        <v>0</v>
+      </c>
       <c r="I39" s="9" t="s">
         <v>116</v>
       </c>
@@ -2558,7 +2575,7 @@
         <v>4</v>
       </c>
       <c r="E40" s="18" t="n">
-        <f aca="false">$E$49*D40</f>
+        <f aca="false">$E$50*D40</f>
         <v>20</v>
       </c>
       <c r="F40" s="33"/>
@@ -2580,15 +2597,18 @@
         <v>119</v>
       </c>
       <c r="D41" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" s="18" t="n">
+        <f aca="false">$E$50*D41</f>
         <v>20</v>
-      </c>
-      <c r="E41" s="18" t="n">
-        <f aca="false">$E$49*D41</f>
-        <v>100</v>
       </c>
       <c r="F41" s="33"/>
       <c r="G41" s="32"/>
       <c r="H41" s="13"/>
+      <c r="I41" s="9" t="s">
+        <v>120</v>
+      </c>
       <c r="J41" s="20"/>
       <c r="K41" s="21"/>
       <c r="L41" s="21"/>
@@ -2599,13 +2619,13 @@
         <v>20</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D42" s="18" t="n">
         <v>20</v>
       </c>
       <c r="E42" s="18" t="n">
-        <f aca="false">$E$49*D42</f>
+        <f aca="false">$E$50*D42</f>
         <v>100</v>
       </c>
       <c r="F42" s="33"/>
@@ -2621,13 +2641,13 @@
         <v>20</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D43" s="18" t="n">
         <v>20</v>
       </c>
       <c r="E43" s="18" t="n">
-        <f aca="false">$E$49*D43</f>
+        <f aca="false">$E$50*D43</f>
         <v>100</v>
       </c>
       <c r="F43" s="33"/>
@@ -2639,173 +2659,176 @@
       <c r="N43" s="10"/>
     </row>
     <row r="44" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="34" t="s">
         <v>20</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E44" s="18" t="n">
-        <f aca="false">$E$49*D44</f>
-        <v>15</v>
-      </c>
-      <c r="F44" s="33" t="n">
-        <v>9</v>
-      </c>
+        <f aca="false">$E$50*D44</f>
+        <v>100</v>
+      </c>
+      <c r="F44" s="33"/>
       <c r="G44" s="32"/>
       <c r="H44" s="13"/>
       <c r="J44" s="20"/>
       <c r="K44" s="21"/>
-      <c r="L44" s="21" t="s">
-        <v>26</v>
-      </c>
+      <c r="L44" s="21"/>
       <c r="N44" s="10"/>
     </row>
-    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="9"/>
+    <row r="45" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E45" s="18" t="n">
-        <f aca="false">$E$49*D45</f>
-        <v>5</v>
+        <f aca="false">$E$50*D45</f>
+        <v>15</v>
       </c>
       <c r="F45" s="33" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="G45" s="32"/>
       <c r="H45" s="13"/>
-      <c r="I45" s="9"/>
       <c r="J45" s="20"/>
       <c r="K45" s="21"/>
       <c r="L45" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="M45" s="9"/>
+        <v>27</v>
+      </c>
       <c r="N45" s="10"/>
-      <c r="O45" s="9"/>
-      <c r="P45" s="9"/>
-      <c r="Q45" s="9"/>
-      <c r="R45" s="9"/>
-      <c r="S45" s="9"/>
-      <c r="T45" s="9"/>
-      <c r="U45" s="9"/>
-      <c r="V45" s="9"/>
-      <c r="W45" s="9"/>
-      <c r="X45" s="9"/>
-      <c r="Y45" s="9"/>
-      <c r="Z45" s="9"/>
-      <c r="AA45" s="9"/>
-      <c r="AB45" s="9"/>
-      <c r="AC45" s="9"/>
-    </row>
-    <row r="46" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1"/>
+    </row>
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="9"/>
       <c r="B46" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D46" s="35" t="n">
+      <c r="C46" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="D46" s="18" t="n">
         <v>1</v>
       </c>
       <c r="E46" s="18" t="n">
-        <f aca="false">$E$49*D46</f>
+        <f aca="false">$E$50*D46</f>
         <v>5</v>
       </c>
-      <c r="F46" s="1" t="n">
+      <c r="F46" s="33" t="n">
         <v>19</v>
       </c>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="13"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="20"/>
+      <c r="K46" s="21"/>
       <c r="L46" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
-      <c r="P46" s="1"/>
-      <c r="Q46" s="1"/>
-      <c r="R46" s="1"/>
-      <c r="S46" s="1"/>
-      <c r="T46" s="1"/>
-      <c r="U46" s="1"/>
-      <c r="V46" s="1"/>
-      <c r="W46" s="1"/>
-      <c r="X46" s="1"/>
-      <c r="Y46" s="1"/>
-      <c r="Z46" s="1"/>
-      <c r="AA46" s="1"/>
-      <c r="AB46" s="1"/>
-      <c r="AC46" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="M46" s="9"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="9"/>
+      <c r="P46" s="9"/>
+      <c r="Q46" s="9"/>
+      <c r="R46" s="9"/>
+      <c r="S46" s="9"/>
+      <c r="T46" s="9"/>
+      <c r="U46" s="9"/>
+      <c r="V46" s="9"/>
+      <c r="W46" s="9"/>
+      <c r="X46" s="9"/>
+      <c r="Y46" s="9"/>
+      <c r="Z46" s="9"/>
+      <c r="AA46" s="9"/>
+      <c r="AB46" s="9"/>
+      <c r="AC46" s="9"/>
     </row>
     <row r="47" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1"/>
       <c r="B47" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C47" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="D47" s="33" t="s">
+      <c r="C47" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E47" s="33"/>
-      <c r="F47" s="33"/>
-      <c r="G47" s="32" t="n">
+      <c r="D47" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="18" t="n">
+        <f aca="false">$E$50*D47</f>
+        <v>5</v>
+      </c>
+      <c r="F47" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="O47" s="1"/>
+      <c r="P47" s="1"/>
+      <c r="Q47" s="1"/>
+      <c r="R47" s="1"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="1"/>
+      <c r="U47" s="1"/>
+      <c r="V47" s="1"/>
+      <c r="W47" s="1"/>
+      <c r="X47" s="1"/>
+      <c r="Y47" s="1"/>
+      <c r="Z47" s="1"/>
+      <c r="AA47" s="1"/>
+      <c r="AB47" s="1"/>
+      <c r="AC47" s="1"/>
+    </row>
+    <row r="48" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D48" s="33" t="s">
+        <v>128</v>
+      </c>
+      <c r="E48" s="33"/>
+      <c r="F48" s="33"/>
+      <c r="G48" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H47" s="13" t="n">
-        <f aca="false">E47*G47</f>
+      <c r="H48" s="13" t="n">
+        <f aca="false">E48*G48</f>
         <v>0</v>
       </c>
-      <c r="J47" s="20"/>
-      <c r="K47" s="21"/>
-      <c r="L47" s="21"/>
-      <c r="N47" s="10" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="9"/>
-      <c r="B48" s="10"/>
-      <c r="C48" s="36"/>
-      <c r="D48" s="37"/>
-      <c r="E48" s="37"/>
-      <c r="F48" s="37"/>
-      <c r="G48" s="32"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="9"/>
-      <c r="J48" s="38"/>
-      <c r="K48" s="39"/>
-      <c r="L48" s="39"/>
-      <c r="N48" s="40"/>
+      <c r="J48" s="20"/>
+      <c r="K48" s="21"/>
+      <c r="L48" s="21"/>
+      <c r="N48" s="10" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="9"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="D49" s="41"/>
-      <c r="E49" s="41" t="n">
-        <v>5</v>
-      </c>
-      <c r="F49" s="41"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="9"/>
+      <c r="B49" s="10"/>
+      <c r="C49" s="36"/>
+      <c r="D49" s="37"/>
+      <c r="E49" s="37"/>
+      <c r="F49" s="37"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="13"/>
       <c r="I49" s="9"/>
       <c r="J49" s="38"/>
       <c r="K49" s="39"/>
@@ -2816,16 +2839,15 @@
       <c r="A50" s="9"/>
       <c r="B50" s="9"/>
       <c r="C50" s="41" t="s">
-        <v>129</v>
-      </c>
-      <c r="D50" s="42"/>
-      <c r="E50" s="42"/>
-      <c r="F50" s="42"/>
-      <c r="G50" s="43"/>
-      <c r="H50" s="43" t="n">
-        <f aca="false">SUM(H2:H37)</f>
-        <v>720.995</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="D50" s="41"/>
+      <c r="E50" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="F50" s="41"/>
+      <c r="G50" s="9"/>
+      <c r="H50" s="9"/>
       <c r="I50" s="9"/>
       <c r="J50" s="38"/>
       <c r="K50" s="39"/>
@@ -2835,12 +2857,17 @@
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="9"/>
       <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="44"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
-      <c r="H51" s="9"/>
+      <c r="C51" s="41" t="s">
+        <v>131</v>
+      </c>
+      <c r="D51" s="42"/>
+      <c r="E51" s="42"/>
+      <c r="F51" s="42"/>
+      <c r="G51" s="43"/>
+      <c r="H51" s="43" t="n">
+        <f aca="false">SUM(H2:H38)</f>
+        <v>737.795</v>
+      </c>
       <c r="I51" s="9"/>
       <c r="J51" s="38"/>
       <c r="K51" s="39"/>
@@ -2848,24 +2875,32 @@
       <c r="N51" s="40"/>
     </row>
     <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C52" s="45" t="s">
-        <v>130</v>
-      </c>
-      <c r="D52" s="46"/>
-      <c r="E52" s="45"/>
-      <c r="F52" s="45"/>
-      <c r="G52" s="45"/>
-      <c r="H52" s="47" t="n">
-        <f aca="false">H50/E49</f>
-        <v>144.199</v>
-      </c>
-      <c r="J52" s="48"/>
-      <c r="K52" s="49"/>
-      <c r="L52" s="49"/>
+      <c r="A52" s="9"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="44"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="9"/>
+      <c r="G52" s="9"/>
+      <c r="H52" s="9"/>
+      <c r="I52" s="9"/>
+      <c r="J52" s="38"/>
+      <c r="K52" s="39"/>
+      <c r="L52" s="39"/>
       <c r="N52" s="40"/>
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D53" s="50"/>
+      <c r="C53" s="45" t="s">
+        <v>132</v>
+      </c>
+      <c r="D53" s="46"/>
+      <c r="E53" s="45"/>
+      <c r="F53" s="45"/>
+      <c r="G53" s="45"/>
+      <c r="H53" s="47" t="n">
+        <f aca="false">H51/E50</f>
+        <v>147.559</v>
+      </c>
       <c r="J53" s="48"/>
       <c r="K53" s="49"/>
       <c r="L53" s="49"/>
@@ -2893,6 +2928,7 @@
       <c r="N56" s="40"/>
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D57" s="50"/>
       <c r="J57" s="48"/>
       <c r="K57" s="49"/>
       <c r="L57" s="49"/>
@@ -8652,34 +8688,40 @@
       <c r="L1016" s="49"/>
       <c r="N1016" s="40"/>
     </row>
+    <row r="1017" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J1017" s="48"/>
+      <c r="K1017" s="49"/>
+      <c r="L1017" s="49"/>
+      <c r="N1017" s="40"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="N8:R8"/>
-    <mergeCell ref="N11:T11"/>
+    <mergeCell ref="N9:R9"/>
+    <mergeCell ref="N12:T12"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="N9" r:id="rId2" display="https://au.element14.com/wurth-elektronik/61900113722dec/contact-2-54mm-crimp-awg28-22/dp/1841425?ost=1841425"/>
-    <hyperlink ref="N11" r:id="rId3" display="https://core-electronics.com.au/5v-step-up-step-down-voltage-regulator-w-adjustable-low-voltage-cutoff-s9v11f5s6cma.html"/>
-    <hyperlink ref="N12" r:id="rId4" display="https://au.element14.com/nidec-copal/mfs101d-8-z/slide-switch-spdt-2a-30vac-th/dp/2854844"/>
-    <hyperlink ref="N13" r:id="rId5" display="https://au.element14.com/schurter/0034-1518/fuse-fast-acting-glass-1-6a/dp/1360787"/>
-    <hyperlink ref="N14" r:id="rId6" display="https://au.element14.com/multicomp-pro/2212s-02sg-85/receptacle-tht-vertical-2-54mm/dp/1593458"/>
-    <hyperlink ref="N15" r:id="rId7" display="https://au.element14.com/multicomp/2212s-04sg-85/socket-pcb-1-row-4way/dp/1593460?ost=1593460"/>
-    <hyperlink ref="N16" r:id="rId8" display="https://au.element14.com/multicomp-pro/2212s-05sg-85/socket-pcb-1-row-5way/dp/1593461"/>
-    <hyperlink ref="N17" r:id="rId9" display="https://au.element14.com/multicomp-pro/2212s-08sg-85/socket-pcb-1-row-8way/dp/1593463?ost=1593463"/>
-    <hyperlink ref="N18" r:id="rId10" display="https://au.element14.com/wurth-elektronik/61900211021/header-2-54mm-r-a-b-locking-2way/dp/1841368?ost=1841368"/>
-    <hyperlink ref="N19" r:id="rId11" display="https://au.element14.com/wurth-elektronik/61900211121/header-2-54mm-locking-2way/dp/1841369"/>
-    <hyperlink ref="N20" r:id="rId12" display="https://au.element14.com/wurth-elektronik/61900211621/housing-2-54mm-2way/dp/1841370?ost=1841370"/>
-    <hyperlink ref="N21" r:id="rId13" display="https://au.element14.com/wurth-elektronik/61900411121/header-2-54mm-locking-4way/dp/1841378?ost=1841378"/>
-    <hyperlink ref="N22" r:id="rId14" display="https://au.element14.com/wurth-elektronik/61900411621/housing-2-54mm-4way/dp/1841379?ost=1841379"/>
-    <hyperlink ref="N23" r:id="rId15" display="https://au.element14.com/wurth-elektronik/61900511121/header-2-54mm-locking-5way/dp/1841382?ost=1841382"/>
-    <hyperlink ref="N24" r:id="rId16" display="https://au.element14.com/wurth-elektronik/61900511621/housing-2-54mm-5way/dp/1841383?ost=1841383"/>
-    <hyperlink ref="N25" r:id="rId17" display="https://au.element14.com/wurth-elektronik/61900811021/conn-r-a-header-8pos-1row-2-54mm/dp/3818035"/>
-    <hyperlink ref="N26" r:id="rId18" display="https://au.element14.com/wurth-elektronik/61900811621/connector-housing-rcpt-8pos-2/dp/3818418?ost=3818418"/>
-    <hyperlink ref="N27" r:id="rId19" display="https://au.element14.com/multicomp-pro/mcdts6-1k/tactile-switch-4-3mm-100g/dp/9471677?ost=mcdts6-1k"/>
-    <hyperlink ref="N28" r:id="rId20" display="https://au.element14.com/multicomp/test-1-bk/test-pin-pcb-black-pk100/dp/1702000"/>
-    <hyperlink ref="N29" r:id="rId21" display="https://au.element14.com/schurter/0751-0110/fuse-clip-5x20mm-pcb-mount/dp/1453528"/>
-    <hyperlink ref="N32" r:id="rId22" display="https://au.element14.com/vishay/k104z15y5ve5tl2/bc-components-part-number/dp/3322180"/>
-    <hyperlink ref="N34" r:id="rId23" display="https://au.element14.com/vishay/k104z15y5ve5tl2/cap-0-1uf-25v-mlcc-radial/dp/3289392"/>
+    <hyperlink ref="N10" r:id="rId2" display="https://au.element14.com/wurth-elektronik/61900113722dec/contact-2-54mm-crimp-awg28-22/dp/1841425?ost=1841425"/>
+    <hyperlink ref="N12" r:id="rId3" display="https://core-electronics.com.au/5v-step-up-step-down-voltage-regulator-w-adjustable-low-voltage-cutoff-s9v11f5s6cma.html"/>
+    <hyperlink ref="N13" r:id="rId4" display="https://au.element14.com/nidec-copal/mfs101d-8-z/slide-switch-spdt-2a-30vac-th/dp/2854844"/>
+    <hyperlink ref="N14" r:id="rId5" display="https://au.element14.com/schurter/0034-1518/fuse-fast-acting-glass-1-6a/dp/1360787"/>
+    <hyperlink ref="N15" r:id="rId6" display="https://au.element14.com/multicomp-pro/2212s-02sg-85/receptacle-tht-vertical-2-54mm/dp/1593458"/>
+    <hyperlink ref="N16" r:id="rId7" display="https://au.element14.com/multicomp/2212s-04sg-85/socket-pcb-1-row-4way/dp/1593460?ost=1593460"/>
+    <hyperlink ref="N17" r:id="rId8" display="https://au.element14.com/multicomp-pro/2212s-05sg-85/socket-pcb-1-row-5way/dp/1593461"/>
+    <hyperlink ref="N18" r:id="rId9" display="https://au.element14.com/multicomp-pro/2212s-08sg-85/socket-pcb-1-row-8way/dp/1593463?ost=1593463"/>
+    <hyperlink ref="N19" r:id="rId10" display="https://au.element14.com/wurth-elektronik/61900211021/header-2-54mm-r-a-b-locking-2way/dp/1841368?ost=1841368"/>
+    <hyperlink ref="N20" r:id="rId11" display="https://au.element14.com/wurth-elektronik/61900211121/header-2-54mm-locking-2way/dp/1841369"/>
+    <hyperlink ref="N21" r:id="rId12" display="https://au.element14.com/wurth-elektronik/61900211621/housing-2-54mm-2way/dp/1841370?ost=1841370"/>
+    <hyperlink ref="N22" r:id="rId13" display="https://au.element14.com/wurth-elektronik/61900411121/header-2-54mm-locking-4way/dp/1841378?ost=1841378"/>
+    <hyperlink ref="N23" r:id="rId14" display="https://au.element14.com/wurth-elektronik/61900411621/housing-2-54mm-4way/dp/1841379?ost=1841379"/>
+    <hyperlink ref="N24" r:id="rId15" display="https://au.element14.com/wurth-elektronik/61900511121/header-2-54mm-locking-5way/dp/1841382?ost=1841382"/>
+    <hyperlink ref="N25" r:id="rId16" display="https://au.element14.com/wurth-elektronik/61900511621/housing-2-54mm-5way/dp/1841383?ost=1841383"/>
+    <hyperlink ref="N26" r:id="rId17" display="https://au.element14.com/wurth-elektronik/61900811021/conn-r-a-header-8pos-1row-2-54mm/dp/3818035"/>
+    <hyperlink ref="N27" r:id="rId18" display="https://au.element14.com/wurth-elektronik/61900811621/connector-housing-rcpt-8pos-2/dp/3818418?ost=3818418"/>
+    <hyperlink ref="N28" r:id="rId19" display="https://au.element14.com/multicomp-pro/mcdts6-1k/tactile-switch-4-3mm-100g/dp/9471677?ost=mcdts6-1k"/>
+    <hyperlink ref="N29" r:id="rId20" display="https://au.element14.com/multicomp/test-1-bk/test-pin-pcb-black-pk100/dp/1702000"/>
+    <hyperlink ref="N30" r:id="rId21" display="https://au.element14.com/schurter/0751-0110/fuse-clip-5x20mm-pcb-mount/dp/1453528"/>
+    <hyperlink ref="N33" r:id="rId22" display="https://au.element14.com/vishay/k104z15y5ve5tl2/bc-components-part-number/dp/3322180"/>
+    <hyperlink ref="N35" r:id="rId23" display="https://au.element14.com/vishay/k104z15y5ve5tl2/cap-0-1uf-25v-mlcc-radial/dp/3289392"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
